--- a/Side Bar Files/GWD Data/GI With Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/GI With Trench PRICE.xlsx
@@ -291,7 +291,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_3" displayName="Table_3" ref="A1:D9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_5" displayName="Table_5" ref="A1:D9">
   <tableColumns count="4">
     <tableColumn id="1" name="Spec Code"/>
     <tableColumn id="2" name="Specification"/>
@@ -598,7 +598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B59D7D2C-8DEB-402D-81B0-E37091D2B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{226EB202-CA7B-495C-988F-7EA059C7B9A7}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/GI With Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/GI With Trench PRICE.xlsx
@@ -136,25 +136,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -172,11 +158,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -598,7 +584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{226EB202-CA7B-495C-988F-7EA059C7B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BC5F86-6753-4248-87D6-C7EC769CBAA6}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/GI With Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/GI With Trench PRICE.xlsx
@@ -584,7 +584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BC5F86-6753-4248-87D6-C7EC769CBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1174F3F3-2DEB-4D0D-845C-2DFA0D9DBAA6}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/GI With Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/GI With Trench PRICE.xlsx
@@ -584,7 +584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1174F3F3-2DEB-4D0D-845C-2DFA0D9DBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B27EE165-3630-448E-9298-5DDC58E6BAA6}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
